--- a/Project-roadmap_YZ.xlsx
+++ b/Project-roadmap_YZ.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14D88F8D-1E1A-41AC-901D-F46AF4744E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4F0FEA-92CE-44C0-B8A4-1A23AEBD2189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="0" windowWidth="19365" windowHeight="20985" tabRatio="605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18585" yWindow="0" windowWidth="19920" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Roadmap" sheetId="10" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
   <si>
     <t>30 de marzo, 2026</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>Pacific GuestHub - Sistema de Reservas</t>
-  </si>
-  <si>
-    <t>Épica 1: Gestion de reservas (core)</t>
   </si>
   <si>
     <t>Yolzer</t>
@@ -84,19 +81,10 @@
     <t>Nombre Proyecto</t>
   </si>
   <si>
-    <t>Épica 2: Experiencia Digital</t>
-  </si>
-  <si>
-    <t>Épica 3: Administración y Reportes</t>
-  </si>
-  <si>
     <t xml:space="preserve">      Hito 2: Validación Técnica</t>
   </si>
   <si>
     <t xml:space="preserve">      Hito 3: Entrega Final y cierre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Hito 1: Validación Sprint 1 &amp; 2</t>
   </si>
   <si>
     <t>Inicio</t>
@@ -114,26 +102,35 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>=Sprint 1 (reservas)</t>
+    <t>Fase 1: Planificación y Requerimientos</t>
   </si>
   <si>
-    <t>=Sprint 2 (digital)</t>
+    <t>Fase 2: Arquitectura UML y Prototipado UX</t>
   </si>
   <si>
-    <t>=Sprint 3 (admin)</t>
+    <t>Fase 3: Validación y Entrega de Diseño (Hito)</t>
   </si>
   <si>
-    <t>Linea de Tiempo de Proyecto (3 Semanas)</t>
+    <t>Completado</t>
   </si>
   <si>
-    <t xml:space="preserve"> =Milestone (sprint Review)</t>
+    <t>Fase 4: Construcción Front-end (React)</t>
+  </si>
+  <si>
+    <t>Fase 5: Desarrollo Back-end y API (Firebase)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Hito 1: "Entrega de Propuesta de Diseño</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =Milestone ( Review)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -270,13 +267,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="0"/>
-      <name val="Bahnschrift SemiBold"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Bahnschrift SemiBold"/>
@@ -289,7 +279,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -410,8 +400,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -629,6 +625,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -674,22 +705,12 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -697,7 +718,10 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -718,15 +742,32 @@
     <xf numFmtId="0" fontId="19" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -868,74 +909,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>460513</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>660538</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="Flowchart: Decision 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DF2F888-FE36-ABCA-127E-665211C6B600}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="460513" y="2894358"/>
-          <a:ext cx="200025" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartDecision">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-CL" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
@@ -1005,81 +978,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Flowchart: Decision 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92398B75-4F7A-4F92-9B0C-AF75C35A6177}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="1619250"/>
-          <a:ext cx="200025" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartDecision">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-CL" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1139,23 +1044,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>122284</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>12379</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>322309</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>136204</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="Flowchart: Decision 13">
+        <xdr:cNvPr id="23" name="Flowchart: Decision 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AF939F0-A5AC-4FBF-A1CC-8EE1F7A4DD9D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{958E5AE3-CD7E-4066-8AEB-01D5AC07352A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1163,7 +1068,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8526265" y="1529052"/>
+          <a:off x="0" y="4459941"/>
           <a:ext cx="200025" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -1207,23 +1112,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>106872</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>19707</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>526676</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>156881</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>306897</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>143532</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>726701</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Flowchart: Decision 14">
+        <xdr:cNvPr id="25" name="Flowchart: Decision 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C74D0E7-C550-44F2-A5A3-01DFC99E45D8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39C19540-6B6E-4F5D-8AFB-BC9E18FB9C21}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1231,7 +1136,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14321103" y="1536380"/>
+          <a:off x="526676" y="3204881"/>
           <a:ext cx="200025" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -1275,23 +1180,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>150833</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>33603</xdr:rowOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>350858</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>157428</xdr:rowOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="Flowchart: Decision 15">
+        <xdr:cNvPr id="26" name="Flowchart: Decision 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1542FABB-81E5-4543-A976-6D92DFDA4001}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6863E77C-941F-4DED-A6B3-7619E5871624}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1299,7 +1204,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11236468" y="1711468"/>
+          <a:off x="18243176" y="1479176"/>
           <a:ext cx="200025" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -1343,23 +1248,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>114957</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>18949</xdr:rowOff>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>314982</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>142774</xdr:rowOff>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="Flowchart: Decision 16">
+        <xdr:cNvPr id="27" name="Flowchart: Decision 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D5C5145-0602-4783-8DDB-09A6EFCFF416}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4CCDB8B-2C10-4BDB-B372-C1AC5A02BD64}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1367,7 +1272,279 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14329188" y="1858007"/>
+          <a:off x="18556941" y="1479176"/>
+          <a:ext cx="200025" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-CL" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>78</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>78</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Flowchart: Decision 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49B735FD-18C0-486D-9E04-984968CDAE20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28597412" y="1949824"/>
+          <a:ext cx="200025" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-CL" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>84</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>84</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Flowchart: Decision 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60379D54-95E1-49D4-A4A6-72675FDE5D36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30480000" y="1949824"/>
+          <a:ext cx="200025" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-CL" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>85</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>85</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="Flowchart: Decision 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85C29DC1-570D-4111-80EE-55FB8947E3A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30793765" y="2106706"/>
+          <a:ext cx="200025" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-CL" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>92</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>92</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Flowchart: Decision 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA2F57D5-32B7-40C7-B713-7336DF1F9BDA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="32990118" y="2106706"/>
           <a:ext cx="200025" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
@@ -1699,490 +1876,1586 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04FD0A9E-4CAD-495E-99FC-B6984EDAADA3}">
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:CO21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="8" max="26" width="5.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="8" max="93" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:93" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+    </row>
+    <row r="2" spans="1:93" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+    </row>
+    <row r="3" spans="1:93" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="H3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB3" s="15"/>
+      <c r="AC3" s="15"/>
+      <c r="AD3" s="15"/>
+      <c r="AE3" s="15"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH3" s="15"/>
+      <c r="AI3" s="15"/>
+      <c r="AJ3" s="15"/>
+      <c r="AK3" s="15"/>
+      <c r="AL3" s="16"/>
+      <c r="AM3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN3" s="15"/>
+      <c r="AO3" s="15"/>
+      <c r="AP3" s="15"/>
+      <c r="AQ3" s="15"/>
+      <c r="AR3" s="15"/>
+      <c r="AS3" s="16"/>
+      <c r="AT3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AU3" s="15"/>
+      <c r="AV3" s="15"/>
+      <c r="AW3" s="15"/>
+      <c r="AX3" s="15"/>
+      <c r="AY3" s="16"/>
+      <c r="AZ3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="BA3" s="15"/>
+      <c r="BB3" s="15"/>
+      <c r="BC3" s="15"/>
+      <c r="BD3" s="15"/>
+      <c r="BE3" s="16"/>
+      <c r="BF3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="BG3" s="15"/>
+      <c r="BH3" s="15"/>
+      <c r="BI3" s="15"/>
+      <c r="BJ3" s="15"/>
+      <c r="BK3" s="16"/>
+      <c r="BL3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="BM3" s="15"/>
+      <c r="BN3" s="15"/>
+      <c r="BO3" s="15"/>
+      <c r="BP3" s="15"/>
+      <c r="BQ3" s="16"/>
+      <c r="BR3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="BS3" s="15"/>
+      <c r="BT3" s="15"/>
+      <c r="BU3" s="15"/>
+      <c r="BV3" s="15"/>
+      <c r="BW3" s="16"/>
+      <c r="BX3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="BY3" s="15"/>
+      <c r="BZ3" s="15"/>
+      <c r="CA3" s="15"/>
+      <c r="CB3" s="15"/>
+      <c r="CC3" s="16"/>
+      <c r="CD3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="CE3" s="15"/>
+      <c r="CF3" s="15"/>
+      <c r="CG3" s="15"/>
+      <c r="CH3" s="15"/>
+      <c r="CI3" s="16"/>
+      <c r="CJ3" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="CK3" s="27"/>
+      <c r="CL3" s="27"/>
+      <c r="CM3" s="27"/>
+      <c r="CN3" s="27"/>
+      <c r="CO3" s="27"/>
+    </row>
+    <row r="4" spans="1:93" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H4" s="17"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="18"/>
+      <c r="V4" s="18"/>
+      <c r="W4" s="18"/>
+      <c r="X4" s="18"/>
+      <c r="Y4" s="18"/>
+      <c r="Z4" s="19"/>
+      <c r="AA4" s="17"/>
+      <c r="AB4" s="18"/>
+      <c r="AC4" s="18"/>
+      <c r="AD4" s="18"/>
+      <c r="AE4" s="18"/>
+      <c r="AF4" s="19"/>
+      <c r="AG4" s="17"/>
+      <c r="AH4" s="18"/>
+      <c r="AI4" s="18"/>
+      <c r="AJ4" s="18"/>
+      <c r="AK4" s="18"/>
+      <c r="AL4" s="19"/>
+      <c r="AM4" s="17"/>
+      <c r="AN4" s="18"/>
+      <c r="AO4" s="18"/>
+      <c r="AP4" s="18"/>
+      <c r="AQ4" s="18"/>
+      <c r="AR4" s="18"/>
+      <c r="AS4" s="19"/>
+      <c r="AT4" s="17"/>
+      <c r="AU4" s="18"/>
+      <c r="AV4" s="18"/>
+      <c r="AW4" s="18"/>
+      <c r="AX4" s="18"/>
+      <c r="AY4" s="19"/>
+      <c r="AZ4" s="17"/>
+      <c r="BA4" s="18"/>
+      <c r="BB4" s="18"/>
+      <c r="BC4" s="18"/>
+      <c r="BD4" s="18"/>
+      <c r="BE4" s="19"/>
+      <c r="BF4" s="17"/>
+      <c r="BG4" s="18"/>
+      <c r="BH4" s="18"/>
+      <c r="BI4" s="18"/>
+      <c r="BJ4" s="18"/>
+      <c r="BK4" s="19"/>
+      <c r="BL4" s="17"/>
+      <c r="BM4" s="18"/>
+      <c r="BN4" s="18"/>
+      <c r="BO4" s="18"/>
+      <c r="BP4" s="18"/>
+      <c r="BQ4" s="19"/>
+      <c r="BR4" s="17"/>
+      <c r="BS4" s="18"/>
+      <c r="BT4" s="18"/>
+      <c r="BU4" s="18"/>
+      <c r="BV4" s="18"/>
+      <c r="BW4" s="19"/>
+      <c r="BX4" s="17"/>
+      <c r="BY4" s="18"/>
+      <c r="BZ4" s="18"/>
+      <c r="CA4" s="18"/>
+      <c r="CB4" s="18"/>
+      <c r="CC4" s="19"/>
+      <c r="CD4" s="17"/>
+      <c r="CE4" s="18"/>
+      <c r="CF4" s="18"/>
+      <c r="CG4" s="18"/>
+      <c r="CH4" s="18"/>
+      <c r="CI4" s="19"/>
+      <c r="CJ4" s="17"/>
+      <c r="CK4" s="18"/>
+      <c r="CL4" s="18"/>
+      <c r="CM4" s="18"/>
+      <c r="CN4" s="18"/>
+      <c r="CO4" s="18"/>
+    </row>
+    <row r="5" spans="1:93" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="12">
+        <v>30</v>
+      </c>
+      <c r="I5" s="12">
+        <v>31</v>
+      </c>
+      <c r="J5" s="12">
+        <v>1</v>
+      </c>
+      <c r="K5" s="12">
+        <v>2</v>
+      </c>
+      <c r="L5" s="12">
+        <v>3</v>
+      </c>
+      <c r="M5" s="12">
+        <v>4</v>
+      </c>
+      <c r="N5" s="12">
+        <v>6</v>
+      </c>
+      <c r="O5" s="12">
+        <v>7</v>
+      </c>
+      <c r="P5" s="12">
+        <v>8</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>9</v>
+      </c>
+      <c r="R5" s="12">
+        <v>10</v>
+      </c>
+      <c r="S5" s="12">
+        <v>11</v>
+      </c>
+      <c r="T5" s="12">
+        <v>13</v>
+      </c>
+      <c r="U5" s="12">
+        <v>14</v>
+      </c>
+      <c r="V5" s="12">
         <v>15</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="W5" s="12">
+        <v>16</v>
+      </c>
+      <c r="X5" s="12">
+        <v>17</v>
+      </c>
+      <c r="Y5" s="12">
+        <v>18</v>
+      </c>
+      <c r="Z5" s="12">
+        <v>19</v>
+      </c>
+      <c r="AA5" s="12">
+        <v>20</v>
+      </c>
+      <c r="AB5" s="12">
+        <v>21</v>
+      </c>
+      <c r="AC5" s="12">
+        <v>22</v>
+      </c>
+      <c r="AD5" s="12">
+        <v>23</v>
+      </c>
+      <c r="AE5" s="12">
+        <v>24</v>
+      </c>
+      <c r="AF5" s="12">
+        <v>25</v>
+      </c>
+      <c r="AG5" s="12">
+        <v>26</v>
+      </c>
+      <c r="AH5" s="12">
+        <v>27</v>
+      </c>
+      <c r="AI5" s="12">
+        <v>28</v>
+      </c>
+      <c r="AJ5" s="12">
+        <v>29</v>
+      </c>
+      <c r="AK5" s="12">
+        <v>30</v>
+      </c>
+      <c r="AL5" s="12">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="12">
         <v>2</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="H1" s="16" t="s">
+      <c r="AN5" s="12">
+        <v>3</v>
+      </c>
+      <c r="AO5" s="12">
+        <v>4</v>
+      </c>
+      <c r="AP5" s="12">
+        <v>6</v>
+      </c>
+      <c r="AQ5" s="12">
+        <v>7</v>
+      </c>
+      <c r="AR5" s="12">
+        <v>8</v>
+      </c>
+      <c r="AS5" s="12">
+        <v>9</v>
+      </c>
+      <c r="AT5" s="12">
+        <v>10</v>
+      </c>
+      <c r="AU5" s="12">
+        <v>11</v>
+      </c>
+      <c r="AV5" s="12">
+        <v>13</v>
+      </c>
+      <c r="AW5" s="12">
+        <v>14</v>
+      </c>
+      <c r="AX5" s="12">
+        <v>15</v>
+      </c>
+      <c r="AY5" s="12">
+        <v>16</v>
+      </c>
+      <c r="AZ5" s="12">
+        <v>17</v>
+      </c>
+      <c r="BA5" s="12">
+        <v>18</v>
+      </c>
+      <c r="BB5" s="12">
+        <v>19</v>
+      </c>
+      <c r="BC5" s="12">
+        <v>20</v>
+      </c>
+      <c r="BD5" s="12">
+        <v>21</v>
+      </c>
+      <c r="BE5" s="12">
+        <v>22</v>
+      </c>
+      <c r="BF5" s="12">
+        <v>23</v>
+      </c>
+      <c r="BG5" s="12">
+        <v>24</v>
+      </c>
+      <c r="BH5" s="12">
+        <v>25</v>
+      </c>
+      <c r="BI5" s="12">
+        <v>26</v>
+      </c>
+      <c r="BJ5" s="12">
+        <v>27</v>
+      </c>
+      <c r="BK5" s="12">
+        <v>28</v>
+      </c>
+      <c r="BL5" s="12">
         <v>29</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
+      <c r="BM5" s="12">
+        <v>30</v>
+      </c>
+      <c r="BN5" s="12">
+        <v>31</v>
+      </c>
+      <c r="BO5" s="12">
+        <v>1</v>
+      </c>
+      <c r="BP5" s="12">
+        <v>2</v>
+      </c>
+      <c r="BQ5" s="12">
+        <v>3</v>
+      </c>
+      <c r="BR5" s="12">
+        <v>4</v>
+      </c>
+      <c r="BS5" s="12">
+        <v>6</v>
+      </c>
+      <c r="BT5" s="12">
+        <v>7</v>
+      </c>
+      <c r="BU5" s="12">
+        <v>8</v>
+      </c>
+      <c r="BV5" s="12">
+        <v>9</v>
+      </c>
+      <c r="BW5" s="12">
+        <v>10</v>
+      </c>
+      <c r="BX5" s="12">
+        <v>11</v>
+      </c>
+      <c r="BY5" s="12">
+        <v>13</v>
+      </c>
+      <c r="BZ5" s="12">
+        <v>14</v>
+      </c>
+      <c r="CA5" s="12">
+        <v>15</v>
+      </c>
+      <c r="CB5" s="12">
+        <v>16</v>
+      </c>
+      <c r="CC5" s="12">
+        <v>17</v>
+      </c>
+      <c r="CD5" s="12">
+        <v>18</v>
+      </c>
+      <c r="CE5" s="12">
+        <v>19</v>
+      </c>
+      <c r="CF5" s="12">
+        <v>20</v>
+      </c>
+      <c r="CG5" s="12">
+        <v>21</v>
+      </c>
+      <c r="CH5" s="12">
+        <v>22</v>
+      </c>
+      <c r="CI5" s="12">
+        <v>23</v>
+      </c>
+      <c r="CJ5" s="12">
+        <v>24</v>
+      </c>
+      <c r="CK5" s="12">
+        <v>25</v>
+      </c>
+      <c r="CL5" s="12">
+        <v>26</v>
+      </c>
+      <c r="CM5" s="12">
+        <v>27</v>
+      </c>
+      <c r="CN5" s="12">
+        <v>28</v>
+      </c>
+      <c r="CO5" s="12">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
+    <row r="6" spans="1:93" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13"/>
+      <c r="AF6" s="13"/>
+      <c r="AG6" s="13"/>
+      <c r="AH6" s="13"/>
+      <c r="AI6" s="13"/>
+      <c r="AJ6" s="13"/>
+      <c r="AK6" s="13"/>
+      <c r="AL6" s="13"/>
+      <c r="AM6" s="13"/>
+      <c r="AN6" s="13"/>
+      <c r="AO6" s="13"/>
+      <c r="AP6" s="13"/>
+      <c r="AQ6" s="13"/>
+      <c r="AR6" s="13"/>
+      <c r="AS6" s="13"/>
+      <c r="AT6" s="13"/>
+      <c r="AU6" s="13"/>
+      <c r="AV6" s="13"/>
+      <c r="AW6" s="13"/>
+      <c r="AX6" s="13"/>
+      <c r="AY6" s="13"/>
+      <c r="AZ6" s="13"/>
+      <c r="BA6" s="13"/>
+      <c r="BB6" s="13"/>
+      <c r="BC6" s="13"/>
+      <c r="BD6" s="13"/>
+      <c r="BE6" s="13"/>
+      <c r="BF6" s="13"/>
+      <c r="BG6" s="13"/>
+      <c r="BH6" s="13"/>
+      <c r="BI6" s="13"/>
+      <c r="BJ6" s="13"/>
+      <c r="BK6" s="13"/>
+      <c r="BL6" s="13"/>
+      <c r="BM6" s="13"/>
+      <c r="BN6" s="13"/>
+      <c r="BO6" s="13"/>
+      <c r="BP6" s="13"/>
+      <c r="BQ6" s="13"/>
+      <c r="BR6" s="13"/>
+      <c r="BS6" s="13"/>
+      <c r="BT6" s="13"/>
+      <c r="BU6" s="13"/>
+      <c r="BV6" s="13"/>
+      <c r="BW6" s="13"/>
+      <c r="BX6" s="13"/>
+      <c r="BY6" s="13"/>
+      <c r="BZ6" s="13"/>
+      <c r="CA6" s="13"/>
+      <c r="CB6" s="13"/>
+      <c r="CC6" s="13"/>
+      <c r="CD6" s="13"/>
+      <c r="CE6" s="13"/>
+      <c r="CF6" s="13"/>
+      <c r="CG6" s="13"/>
+      <c r="CH6" s="13"/>
+      <c r="CI6" s="13"/>
+      <c r="CJ6" s="13"/>
+      <c r="CK6" s="13"/>
+      <c r="CL6" s="13"/>
+      <c r="CM6" s="13"/>
+      <c r="CN6" s="13"/>
+      <c r="CO6" s="13"/>
     </row>
-    <row r="3" spans="1:26" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="H3" s="17" t="s">
+    <row r="7" spans="1:93" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46111</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46131</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="8"/>
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="8"/>
+      <c r="AD7" s="8"/>
+      <c r="AE7" s="8"/>
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="8"/>
+      <c r="AH7" s="8"/>
+      <c r="AI7" s="8"/>
+      <c r="AJ7" s="8"/>
+      <c r="AK7" s="8"/>
+      <c r="AL7" s="8"/>
+      <c r="AM7" s="8"/>
+      <c r="AN7" s="8"/>
+      <c r="AO7" s="8"/>
+      <c r="AP7" s="8"/>
+      <c r="AQ7" s="8"/>
+      <c r="AR7" s="8"/>
+      <c r="AS7" s="8"/>
+      <c r="AT7" s="8"/>
+      <c r="AU7" s="8"/>
+      <c r="AV7" s="8"/>
+      <c r="AW7" s="8"/>
+      <c r="AX7" s="8"/>
+      <c r="AY7" s="8"/>
+      <c r="AZ7" s="8"/>
+      <c r="BA7" s="8"/>
+      <c r="BB7" s="8"/>
+      <c r="BC7" s="8"/>
+      <c r="BD7" s="8"/>
+      <c r="BE7" s="8"/>
+      <c r="BF7" s="8"/>
+      <c r="BG7" s="8"/>
+      <c r="BH7" s="8"/>
+      <c r="BI7" s="8"/>
+      <c r="BJ7" s="8"/>
+      <c r="BK7" s="8"/>
+      <c r="BL7" s="8"/>
+      <c r="BM7" s="8"/>
+      <c r="BN7" s="8"/>
+      <c r="BO7" s="8"/>
+      <c r="BP7" s="8"/>
+      <c r="BQ7" s="8"/>
+      <c r="BR7" s="8"/>
+      <c r="BS7" s="8"/>
+      <c r="BT7" s="8"/>
+      <c r="BU7" s="8"/>
+      <c r="BV7" s="8"/>
+      <c r="BW7" s="8"/>
+      <c r="BX7" s="8"/>
+      <c r="BY7" s="8"/>
+      <c r="BZ7" s="8"/>
+      <c r="CA7" s="8"/>
+      <c r="CB7" s="8"/>
+      <c r="CC7" s="8"/>
+      <c r="CD7" s="8"/>
+      <c r="CE7" s="8"/>
+      <c r="CF7" s="8"/>
+      <c r="CG7" s="8"/>
+      <c r="CH7" s="8"/>
+      <c r="CI7" s="8"/>
+      <c r="CJ7" s="8"/>
+      <c r="CK7" s="8"/>
+      <c r="CL7" s="8"/>
+      <c r="CM7" s="8"/>
+      <c r="CN7" s="8"/>
+      <c r="CO7" s="8"/>
+    </row>
+    <row r="8" spans="1:93" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="17" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46132</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46145</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="9"/>
+      <c r="AG8" s="9"/>
+      <c r="AH8" s="9"/>
+      <c r="AI8" s="9"/>
+      <c r="AJ8" s="9"/>
+      <c r="AK8" s="9"/>
+      <c r="AL8" s="9"/>
+      <c r="AM8" s="9"/>
+      <c r="AN8" s="9"/>
+      <c r="AO8" s="8"/>
+      <c r="AP8" s="8"/>
+      <c r="AQ8" s="8"/>
+      <c r="AR8" s="8"/>
+      <c r="AS8" s="8"/>
+      <c r="AU8" s="8"/>
+      <c r="AV8" s="8"/>
+      <c r="AW8" s="8"/>
+      <c r="AX8" s="8"/>
+      <c r="AY8" s="8"/>
+      <c r="AZ8" s="8"/>
+      <c r="BA8" s="8"/>
+      <c r="BB8" s="8"/>
+      <c r="BC8" s="8"/>
+      <c r="BD8" s="8"/>
+      <c r="BE8" s="8"/>
+      <c r="BF8" s="8"/>
+      <c r="BG8" s="8"/>
+      <c r="BH8" s="8"/>
+      <c r="BI8" s="8"/>
+      <c r="BJ8" s="8"/>
+      <c r="BK8" s="8"/>
+      <c r="BL8" s="8"/>
+      <c r="BM8" s="8"/>
+      <c r="BN8" s="8"/>
+      <c r="BO8" s="8"/>
+      <c r="BP8" s="8"/>
+      <c r="BQ8" s="8"/>
+      <c r="BR8" s="8"/>
+      <c r="BS8" s="8"/>
+      <c r="BT8" s="8"/>
+      <c r="BU8" s="8"/>
+      <c r="BV8" s="8"/>
+      <c r="BW8" s="8"/>
+      <c r="BX8" s="8"/>
+      <c r="BY8" s="8"/>
+      <c r="BZ8" s="8"/>
+      <c r="CA8" s="8"/>
+      <c r="CB8" s="8"/>
+      <c r="CC8" s="8"/>
+      <c r="CD8" s="8"/>
+      <c r="CE8" s="8"/>
+      <c r="CF8" s="8"/>
+      <c r="CG8" s="8"/>
+      <c r="CH8" s="8"/>
+      <c r="CI8" s="8"/>
+      <c r="CJ8" s="8"/>
+      <c r="CK8" s="8"/>
+      <c r="CL8" s="8"/>
+      <c r="CM8" s="8"/>
+      <c r="CN8" s="8"/>
+      <c r="CO8" s="8"/>
+    </row>
+    <row r="9" spans="1:93" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="18"/>
-      <c r="S3" s="19"/>
-      <c r="T3" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="U3" s="18"/>
-      <c r="V3" s="18"/>
-      <c r="W3" s="18"/>
-      <c r="X3" s="18"/>
-      <c r="Y3" s="18"/>
-      <c r="Z3" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4">
+        <v>46146</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46152</v>
+      </c>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8"/>
+      <c r="AB9" s="8"/>
+      <c r="AC9" s="8"/>
+      <c r="AD9" s="8"/>
+      <c r="AE9" s="8"/>
+      <c r="AF9" s="8"/>
+      <c r="AG9" s="8"/>
+      <c r="AH9" s="8"/>
+      <c r="AI9" s="8"/>
+      <c r="AJ9" s="8"/>
+      <c r="AK9" s="8"/>
+      <c r="AL9" s="8"/>
+      <c r="AM9" s="8"/>
+      <c r="AN9" s="8"/>
+      <c r="AO9" s="9"/>
+      <c r="AP9" s="9"/>
+      <c r="AQ9" s="9"/>
+      <c r="AR9" s="9"/>
+      <c r="AS9" s="9"/>
+      <c r="AT9" s="9"/>
+      <c r="AU9" s="8"/>
+      <c r="AV9" s="8"/>
+      <c r="AW9" s="8"/>
+      <c r="AX9" s="8"/>
+      <c r="AY9" s="8"/>
+      <c r="AZ9" s="8"/>
+      <c r="BA9" s="8"/>
+      <c r="BB9" s="8"/>
+      <c r="BC9" s="8"/>
+      <c r="BD9" s="8"/>
+      <c r="BE9" s="8"/>
+      <c r="BF9" s="8"/>
+      <c r="BG9" s="8"/>
+      <c r="BH9" s="8"/>
+      <c r="BI9" s="8"/>
+      <c r="BJ9" s="8"/>
+      <c r="BK9" s="8"/>
+      <c r="BL9" s="8"/>
+      <c r="BM9" s="8"/>
+      <c r="BN9" s="8"/>
+      <c r="BO9" s="8"/>
+      <c r="BP9" s="8"/>
+      <c r="BQ9" s="8"/>
+      <c r="BR9" s="8"/>
+      <c r="BS9" s="8"/>
+      <c r="BT9" s="8"/>
+      <c r="BU9" s="8"/>
+      <c r="BV9" s="8"/>
+      <c r="BW9" s="8"/>
+      <c r="BX9" s="8"/>
+      <c r="BY9" s="8"/>
+      <c r="BZ9" s="8"/>
+      <c r="CA9" s="8"/>
+      <c r="CB9" s="8"/>
+      <c r="CC9" s="8"/>
+      <c r="CD9" s="8"/>
+      <c r="CE9" s="8"/>
+      <c r="CF9" s="8"/>
+      <c r="CG9" s="8"/>
+      <c r="CH9" s="8"/>
+      <c r="CI9" s="8"/>
+      <c r="CJ9" s="8"/>
+      <c r="CK9" s="8"/>
+      <c r="CL9" s="8"/>
+      <c r="CM9" s="8"/>
+      <c r="CN9" s="8"/>
+      <c r="CO9" s="8"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="H4" s="20"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="21"/>
-      <c r="X4" s="21"/>
-      <c r="Y4" s="21"/>
-      <c r="Z4" s="22"/>
+    <row r="10" spans="1:93" x14ac:dyDescent="0.2">
+      <c r="A10" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="4">
+        <v>46152</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46153</v>
+      </c>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="8"/>
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AH10" s="8"/>
+      <c r="AI10" s="8"/>
+      <c r="AJ10" s="8"/>
+      <c r="AK10" s="8"/>
+      <c r="AL10" s="8"/>
+      <c r="AM10" s="8"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="8"/>
+      <c r="AP10" s="8"/>
+      <c r="AQ10" s="8"/>
+      <c r="AR10" s="8"/>
+      <c r="AS10" s="8"/>
+      <c r="AT10" s="10"/>
+      <c r="AU10" s="10"/>
+      <c r="AV10" s="8"/>
+      <c r="AW10" s="8"/>
+      <c r="AX10" s="8"/>
+      <c r="AY10" s="8"/>
+      <c r="AZ10" s="8"/>
+      <c r="BA10" s="8"/>
+      <c r="BB10" s="8"/>
+      <c r="BC10" s="8"/>
+      <c r="BD10" s="8"/>
+      <c r="BE10" s="8"/>
+      <c r="BF10" s="8"/>
+      <c r="BG10" s="8"/>
+      <c r="BH10" s="8"/>
+      <c r="BI10" s="8"/>
+      <c r="BJ10" s="8"/>
+      <c r="BK10" s="8"/>
+      <c r="BL10" s="8"/>
+      <c r="BM10" s="8"/>
+      <c r="BN10" s="8"/>
+      <c r="BO10" s="8"/>
+      <c r="BP10" s="8"/>
+      <c r="BQ10" s="8"/>
+      <c r="BR10" s="8"/>
+      <c r="BS10" s="8"/>
+      <c r="BT10" s="8"/>
+      <c r="BU10" s="8"/>
+      <c r="BV10" s="8"/>
+      <c r="BW10" s="8"/>
+      <c r="BX10" s="8"/>
+      <c r="BY10" s="8"/>
+      <c r="BZ10" s="8"/>
+      <c r="CA10" s="8"/>
+      <c r="CB10" s="8"/>
+      <c r="CC10" s="8"/>
+      <c r="CD10" s="8"/>
+      <c r="CE10" s="8"/>
+      <c r="CF10" s="8"/>
+      <c r="CG10" s="8"/>
+      <c r="CH10" s="8"/>
+      <c r="CI10" s="8"/>
+      <c r="CJ10" s="8"/>
+      <c r="CK10" s="8"/>
+      <c r="CL10" s="8"/>
+      <c r="CM10" s="8"/>
+      <c r="CN10" s="8"/>
+      <c r="CO10" s="8"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A5" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="23">
-        <v>30</v>
-      </c>
-      <c r="I5" s="23">
-        <v>31</v>
-      </c>
-      <c r="J5" s="23">
-        <v>1</v>
-      </c>
-      <c r="K5" s="23">
-        <v>2</v>
-      </c>
-      <c r="L5" s="23">
+    <row r="11" spans="1:93" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="23">
-        <v>4</v>
-      </c>
-      <c r="N5" s="23">
+      <c r="D11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4">
+        <v>46153</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46166</v>
+      </c>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8"/>
+      <c r="AA11" s="8"/>
+      <c r="AB11" s="8"/>
+      <c r="AC11" s="8"/>
+      <c r="AD11" s="8"/>
+      <c r="AE11" s="8"/>
+      <c r="AF11" s="8"/>
+      <c r="AG11" s="8"/>
+      <c r="AH11" s="8"/>
+      <c r="AI11" s="8"/>
+      <c r="AJ11" s="8"/>
+      <c r="AK11" s="8"/>
+      <c r="AL11" s="8"/>
+      <c r="AM11" s="8"/>
+      <c r="AN11" s="8"/>
+      <c r="AO11" s="8"/>
+      <c r="AP11" s="8"/>
+      <c r="AQ11" s="8"/>
+      <c r="AR11" s="8"/>
+      <c r="AS11" s="8"/>
+      <c r="AT11" s="8"/>
+      <c r="AU11" s="9"/>
+      <c r="AV11" s="9"/>
+      <c r="AW11" s="9"/>
+      <c r="AX11" s="9"/>
+      <c r="AY11" s="9"/>
+      <c r="AZ11" s="9"/>
+      <c r="BA11" s="9"/>
+      <c r="BB11" s="9"/>
+      <c r="BC11" s="9"/>
+      <c r="BD11" s="9"/>
+      <c r="BE11" s="9"/>
+      <c r="BF11" s="9"/>
+      <c r="BG11" s="9"/>
+      <c r="BH11" s="8"/>
+      <c r="BI11" s="8"/>
+      <c r="BJ11" s="8"/>
+      <c r="BK11" s="8"/>
+      <c r="BL11" s="8"/>
+      <c r="BM11" s="8"/>
+      <c r="BN11" s="8"/>
+      <c r="BO11" s="8"/>
+      <c r="BP11" s="8"/>
+      <c r="BQ11" s="8"/>
+      <c r="BR11" s="8"/>
+      <c r="BS11" s="8"/>
+      <c r="BT11" s="8"/>
+      <c r="BU11" s="8"/>
+      <c r="BV11" s="8"/>
+      <c r="BW11" s="8"/>
+      <c r="BX11" s="8"/>
+      <c r="BY11" s="8"/>
+      <c r="BZ11" s="8"/>
+      <c r="CA11" s="8"/>
+      <c r="CB11" s="8"/>
+      <c r="CC11" s="8"/>
+      <c r="CD11" s="8"/>
+      <c r="CE11" s="8"/>
+      <c r="CF11" s="8"/>
+      <c r="CG11" s="8"/>
+      <c r="CH11" s="8"/>
+      <c r="CI11" s="8"/>
+      <c r="CJ11" s="8"/>
+      <c r="CK11" s="8"/>
+      <c r="CL11" s="8"/>
+      <c r="CM11" s="8"/>
+      <c r="CN11" s="8"/>
+      <c r="CO11" s="8"/>
+    </row>
+    <row r="12" spans="1:93" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="4">
+        <v>46167</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46187</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+      <c r="AA12" s="8"/>
+      <c r="AB12" s="8"/>
+      <c r="AC12" s="8"/>
+      <c r="AD12" s="8"/>
+      <c r="AE12" s="8"/>
+      <c r="AF12" s="8"/>
+      <c r="AG12" s="8"/>
+      <c r="AH12" s="8"/>
+      <c r="AI12" s="8"/>
+      <c r="AJ12" s="8"/>
+      <c r="AK12" s="8"/>
+      <c r="AL12" s="8"/>
+      <c r="AM12" s="8"/>
+      <c r="AN12" s="8"/>
+      <c r="AO12" s="8"/>
+      <c r="AP12" s="8"/>
+      <c r="AQ12" s="8"/>
+      <c r="AR12" s="8"/>
+      <c r="AS12" s="8"/>
+      <c r="AT12" s="8"/>
+      <c r="AU12" s="8"/>
+      <c r="AV12" s="8"/>
+      <c r="AW12" s="8"/>
+      <c r="AX12" s="8"/>
+      <c r="AY12" s="8"/>
+      <c r="AZ12" s="8"/>
+      <c r="BA12" s="8"/>
+      <c r="BB12" s="8"/>
+      <c r="BC12" s="8"/>
+      <c r="BD12" s="8"/>
+      <c r="BE12" s="8"/>
+      <c r="BF12" s="8"/>
+      <c r="BG12" s="8"/>
+      <c r="BH12" s="9"/>
+      <c r="BI12" s="9"/>
+      <c r="BJ12" s="9"/>
+      <c r="BK12" s="9"/>
+      <c r="BL12" s="9"/>
+      <c r="BM12" s="9"/>
+      <c r="BN12" s="9"/>
+      <c r="BO12" s="9"/>
+      <c r="BP12" s="9"/>
+      <c r="BQ12" s="9"/>
+      <c r="BR12" s="9"/>
+      <c r="BS12" s="9"/>
+      <c r="BT12" s="9"/>
+      <c r="BU12" s="9"/>
+      <c r="BV12" s="9"/>
+      <c r="BW12" s="9"/>
+      <c r="BX12" s="9"/>
+      <c r="BY12" s="9"/>
+      <c r="BZ12" s="9"/>
+      <c r="CA12" s="8"/>
+      <c r="CB12" s="8"/>
+      <c r="CC12" s="8"/>
+      <c r="CD12" s="8"/>
+      <c r="CE12" s="8"/>
+      <c r="CF12" s="8"/>
+      <c r="CG12" s="8"/>
+      <c r="CH12" s="8"/>
+      <c r="CI12" s="8"/>
+      <c r="CJ12" s="8"/>
+      <c r="CK12" s="8"/>
+      <c r="CL12" s="8"/>
+      <c r="CM12" s="8"/>
+      <c r="CN12" s="8"/>
+      <c r="CO12" s="8"/>
+    </row>
+    <row r="13" spans="1:93" x14ac:dyDescent="0.2">
+      <c r="A13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="4">
+        <v>46188</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46194</v>
+      </c>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="8"/>
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="8"/>
+      <c r="AD13" s="8"/>
+      <c r="AE13" s="8"/>
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="8"/>
+      <c r="AH13" s="8"/>
+      <c r="AI13" s="8"/>
+      <c r="AJ13" s="8"/>
+      <c r="AK13" s="8"/>
+      <c r="AL13" s="8"/>
+      <c r="AM13" s="8"/>
+      <c r="AN13" s="8"/>
+      <c r="AO13" s="8"/>
+      <c r="AP13" s="8"/>
+      <c r="AQ13" s="8"/>
+      <c r="AR13" s="8"/>
+      <c r="AS13" s="8"/>
+      <c r="AT13" s="8"/>
+      <c r="AU13" s="8"/>
+      <c r="AV13" s="8"/>
+      <c r="AW13" s="8"/>
+      <c r="AX13" s="8"/>
+      <c r="AY13" s="8"/>
+      <c r="AZ13" s="8"/>
+      <c r="BA13" s="8"/>
+      <c r="BB13" s="8"/>
+      <c r="BC13" s="8"/>
+      <c r="BD13" s="8"/>
+      <c r="BE13" s="8"/>
+      <c r="BF13" s="8"/>
+      <c r="BG13" s="8"/>
+      <c r="BH13" s="8"/>
+      <c r="BI13" s="8"/>
+      <c r="BJ13" s="8"/>
+      <c r="BK13" s="8"/>
+      <c r="BL13" s="8"/>
+      <c r="BM13" s="8"/>
+      <c r="BN13" s="8"/>
+      <c r="BO13" s="8"/>
+      <c r="BP13" s="8"/>
+      <c r="BQ13" s="8"/>
+      <c r="BR13" s="8"/>
+      <c r="BS13" s="8"/>
+      <c r="BT13" s="8"/>
+      <c r="BU13" s="8"/>
+      <c r="BV13" s="8"/>
+      <c r="BW13" s="8"/>
+      <c r="BX13" s="8"/>
+      <c r="BY13" s="8"/>
+      <c r="BZ13" s="8"/>
+      <c r="CA13" s="11"/>
+      <c r="CB13" s="11"/>
+      <c r="CC13" s="11"/>
+      <c r="CD13" s="11"/>
+      <c r="CE13" s="11"/>
+      <c r="CF13" s="11"/>
+      <c r="CG13" s="11"/>
+      <c r="CH13" s="8"/>
+      <c r="CI13" s="8"/>
+      <c r="CJ13" s="8"/>
+      <c r="CK13" s="8"/>
+      <c r="CL13" s="8"/>
+      <c r="CM13" s="8"/>
+      <c r="CN13" s="8"/>
+      <c r="CO13" s="8"/>
+    </row>
+    <row r="14" spans="1:93" x14ac:dyDescent="0.2">
+      <c r="A14" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="23">
-        <v>7</v>
-      </c>
-      <c r="P5" s="23">
+      <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="23">
-        <v>9</v>
-      </c>
-      <c r="R5" s="23">
-        <v>10</v>
-      </c>
-      <c r="S5" s="23">
-        <v>11</v>
-      </c>
-      <c r="T5" s="23">
-        <v>13</v>
-      </c>
-      <c r="U5" s="23">
-        <v>14</v>
-      </c>
-      <c r="V5" s="23">
-        <v>15</v>
-      </c>
-      <c r="W5" s="23">
-        <v>16</v>
-      </c>
-      <c r="X5" s="23">
-        <v>17</v>
-      </c>
-      <c r="Y5" s="23">
-        <v>18</v>
-      </c>
-      <c r="Z5" s="23">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="24"/>
-      <c r="V6" s="24"/>
-      <c r="W6" s="24"/>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="24"/>
-      <c r="Z6" s="24"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="7">
-        <v>46111</v>
-      </c>
-      <c r="F7" s="7">
-        <v>46116</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="7">
-        <v>46118</v>
-      </c>
-      <c r="F8" s="7">
-        <v>46124</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="7">
-        <v>46125</v>
-      </c>
-      <c r="F9" s="7">
-        <v>46131</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="15"/>
-      <c r="Y9" s="15"/>
-      <c r="Z9" s="15"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="7">
-        <v>46117</v>
-      </c>
-      <c r="F10" s="7">
-        <v>46131</v>
-      </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="12"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="8">
-        <v>46124</v>
-      </c>
-      <c r="F11" s="8">
-        <v>46124</v>
-      </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="12"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="7">
-        <v>46131</v>
-      </c>
-      <c r="F12" s="7">
-        <v>46131</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="12"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="Z13" s="1"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A15" s="10"/>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
-      <c r="B16" t="s">
-        <v>27</v>
-      </c>
+      <c r="E14" s="4">
+        <v>46195</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46202</v>
+      </c>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8"/>
+      <c r="AA14" s="8"/>
+      <c r="AB14" s="8"/>
+      <c r="AC14" s="8"/>
+      <c r="AD14" s="8"/>
+      <c r="AE14" s="8"/>
+      <c r="AF14" s="8"/>
+      <c r="AG14" s="8"/>
+      <c r="AH14" s="8"/>
+      <c r="AI14" s="8"/>
+      <c r="AJ14" s="8"/>
+      <c r="AK14" s="8"/>
+      <c r="AL14" s="8"/>
+      <c r="AM14" s="8"/>
+      <c r="AN14" s="8"/>
+      <c r="AO14" s="8"/>
+      <c r="AP14" s="8"/>
+      <c r="AQ14" s="8"/>
+      <c r="AR14" s="8"/>
+      <c r="AS14" s="8"/>
+      <c r="AT14" s="8"/>
+      <c r="AU14" s="8"/>
+      <c r="AV14" s="8"/>
+      <c r="AW14" s="8"/>
+      <c r="AX14" s="8"/>
+      <c r="AY14" s="8"/>
+      <c r="AZ14" s="8"/>
+      <c r="BA14" s="8"/>
+      <c r="BB14" s="8"/>
+      <c r="BC14" s="8"/>
+      <c r="BD14" s="8"/>
+      <c r="BE14" s="8"/>
+      <c r="BF14" s="8"/>
+      <c r="BG14" s="8"/>
+      <c r="BH14" s="8"/>
+      <c r="BI14" s="8"/>
+      <c r="BJ14" s="8"/>
+      <c r="BK14" s="8"/>
+      <c r="BL14" s="8"/>
+      <c r="BM14" s="8"/>
+      <c r="BN14" s="8"/>
+      <c r="BO14" s="8"/>
+      <c r="BP14" s="8"/>
+      <c r="BQ14" s="8"/>
+      <c r="BR14" s="8"/>
+      <c r="BS14" s="8"/>
+      <c r="BT14" s="8"/>
+      <c r="BU14" s="8"/>
+      <c r="BV14" s="8"/>
+      <c r="BW14" s="8"/>
+      <c r="BX14" s="8"/>
+      <c r="BY14" s="8"/>
+      <c r="BZ14" s="8"/>
+      <c r="CA14" s="8"/>
+      <c r="CB14" s="8"/>
+      <c r="CC14" s="8"/>
+      <c r="CD14" s="8"/>
+      <c r="CE14" s="8"/>
+      <c r="CF14" s="8"/>
+      <c r="CG14" s="8"/>
+      <c r="CH14" s="29"/>
+      <c r="CI14" s="29"/>
+      <c r="CJ14" s="29"/>
+      <c r="CK14" s="29"/>
+      <c r="CL14" s="29"/>
+      <c r="CM14" s="29"/>
+      <c r="CN14" s="29"/>
+      <c r="CO14" s="29"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
+      <c r="A17" s="6"/>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1" t="s">
-        <v>30</v>
+      <c r="A18" s="7"/>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="28"/>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="116">
+    <mergeCell ref="CD3:CI4"/>
+    <mergeCell ref="CJ3:CO4"/>
+    <mergeCell ref="CN5:CN6"/>
+    <mergeCell ref="CO5:CO6"/>
+    <mergeCell ref="CI5:CI6"/>
+    <mergeCell ref="CJ5:CJ6"/>
+    <mergeCell ref="CK5:CK6"/>
+    <mergeCell ref="CL5:CL6"/>
+    <mergeCell ref="CM5:CM6"/>
+    <mergeCell ref="CD5:CD6"/>
+    <mergeCell ref="CE5:CE6"/>
+    <mergeCell ref="CF5:CF6"/>
+    <mergeCell ref="CG5:CG6"/>
+    <mergeCell ref="CH5:CH6"/>
+    <mergeCell ref="BX3:CC4"/>
+    <mergeCell ref="BX5:BX6"/>
+    <mergeCell ref="BY5:BY6"/>
+    <mergeCell ref="BZ5:BZ6"/>
+    <mergeCell ref="CA5:CA6"/>
+    <mergeCell ref="CB5:CB6"/>
+    <mergeCell ref="CC5:CC6"/>
+    <mergeCell ref="BR3:BW4"/>
+    <mergeCell ref="BR5:BR6"/>
+    <mergeCell ref="BS5:BS6"/>
+    <mergeCell ref="BT5:BT6"/>
+    <mergeCell ref="BU5:BU6"/>
+    <mergeCell ref="BV5:BV6"/>
+    <mergeCell ref="BW5:BW6"/>
+    <mergeCell ref="BF3:BK4"/>
+    <mergeCell ref="BL3:BQ4"/>
+    <mergeCell ref="BN5:BN6"/>
+    <mergeCell ref="BO5:BO6"/>
+    <mergeCell ref="BP5:BP6"/>
+    <mergeCell ref="BQ5:BQ6"/>
+    <mergeCell ref="BJ5:BJ6"/>
+    <mergeCell ref="BK5:BK6"/>
+    <mergeCell ref="BL5:BL6"/>
+    <mergeCell ref="BM5:BM6"/>
+    <mergeCell ref="BE5:BE6"/>
+    <mergeCell ref="BF5:BF6"/>
+    <mergeCell ref="BG5:BG6"/>
+    <mergeCell ref="BH5:BH6"/>
+    <mergeCell ref="BI5:BI6"/>
+    <mergeCell ref="AS5:AS6"/>
+    <mergeCell ref="AT3:AY4"/>
+    <mergeCell ref="AZ3:BE4"/>
+    <mergeCell ref="AT5:AT6"/>
+    <mergeCell ref="AU5:AU6"/>
+    <mergeCell ref="AV5:AV6"/>
+    <mergeCell ref="AW5:AW6"/>
+    <mergeCell ref="AX5:AX6"/>
+    <mergeCell ref="AY5:AY6"/>
+    <mergeCell ref="AZ5:AZ6"/>
+    <mergeCell ref="BA5:BA6"/>
+    <mergeCell ref="BB5:BB6"/>
+    <mergeCell ref="BC5:BC6"/>
+    <mergeCell ref="BD5:BD6"/>
+    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AO5:AO6"/>
+    <mergeCell ref="AP5:AP6"/>
+    <mergeCell ref="AQ5:AQ6"/>
+    <mergeCell ref="AR5:AR6"/>
+    <mergeCell ref="AA3:AF4"/>
+    <mergeCell ref="AG3:AL4"/>
+    <mergeCell ref="AM3:AS4"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="AD5:AD6"/>
+    <mergeCell ref="AE5:AE6"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="AK5:AK6"/>
+    <mergeCell ref="AL5:AL6"/>
+    <mergeCell ref="AM5:AM6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
     <mergeCell ref="Y5:Y6"/>
     <mergeCell ref="Z5:Z6"/>
     <mergeCell ref="H3:M4"/>
@@ -2199,27 +3472,6 @@
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="H1:Z2"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
